--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
@@ -938,88 +938,88 @@
     <t>215</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>R$ 4.148,37</t>
-  </si>
-  <si>
-    <t>45.5</t>
-  </si>
-  <si>
-    <t>28.7</t>
-  </si>
-  <si>
-    <t>4.75</t>
-  </si>
-  <si>
-    <t>18.7</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>45.7%</t>
-  </si>
-  <si>
-    <t>17.9%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 4.054,39</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>4.71</t>
+  </si>
+  <si>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>44.6%</t>
+  </si>
+  <si>
+    <t>18.2%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>6.3%</t>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
   </si>
   <si>
     <t>2.6%</t>
   </si>
   <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>1009.0</t>
-  </si>
-  <si>
-    <t>806.0</t>
-  </si>
-  <si>
-    <t>75.0</t>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>1171.0</t>
+  </si>
+  <si>
+    <t>940.0</t>
+  </si>
+  <si>
+    <t>91.0</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>279.0</t>
+  </si>
+  <si>
+    <t>67.0</t>
   </si>
   <si>
     <t>9.0</t>
   </si>
   <si>
-    <t>250.0</t>
-  </si>
-  <si>
-    <t>54.0</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>286.0</t>
-  </si>
-  <si>
-    <t>117.0</t>
-  </si>
-  <si>
-    <t>198.0</t>
-  </si>
-  <si>
-    <t>0.5%</t>
+    <t>347.0</t>
+  </si>
+  <si>
+    <t>133.0</t>
+  </si>
+  <si>
+    <t>223.0</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>22.0</t>
@@ -5171,7 +5171,7 @@
         <v>19540</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C26" s="4">
         <v>51</v>
@@ -5201,35 +5201,93 @@
         <v>58</v>
       </c>
       <c r="L26" s="4"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="6"/>
-      <c r="AE26" s="6"/>
-      <c r="AF26" s="6"/>
-      <c r="AG26" s="6"/>
-      <c r="AH26" s="6"/>
-      <c r="AI26" s="6"/>
-      <c r="AJ26" s="6"/>
-      <c r="AK26" s="6"/>
-      <c r="AL26" s="6"/>
-      <c r="AM26" s="6"/>
-      <c r="AN26" s="9"/>
-      <c r="AO26" s="6"/>
+      <c r="M26" s="5">
+        <v>8829.5799999999999</v>
+      </c>
+      <c r="N26" s="6">
+        <v>86</v>
+      </c>
+      <c r="O26" s="6">
+        <v>55</v>
+      </c>
+      <c r="P26" s="7">
+        <v>3.0263708860759495</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>14.490303636363635</v>
+      </c>
+      <c r="R26" s="8">
+        <v>5.6789999999999994</v>
+      </c>
+      <c r="S26" s="8">
+        <v>7</v>
+      </c>
+      <c r="T26" s="9">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U26" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V26" s="9">
+        <v>0.054545454545454543</v>
+      </c>
+      <c r="W26" s="9">
+        <v>0</v>
+      </c>
+      <c r="X26" s="9">
+        <v>0.14545454545454545</v>
+      </c>
+      <c r="Y26" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Z26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AB26" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AC26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="6">
+        <v>22</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF26" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>8</v>
+      </c>
+      <c r="AI26" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP26" s="4">
         <v>58</v>
       </c>
@@ -5427,7 +5485,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5457,35 +5515,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>2614.29</v>
+      </c>
+      <c r="N28" s="6">
+        <v>31</v>
+      </c>
+      <c r="O28" s="6">
+        <v>17</v>
+      </c>
+      <c r="P28" s="7">
+        <v>2.6397838709677419</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>18.686276470588236</v>
+      </c>
+      <c r="R28" s="8">
+        <v>9.485294117647058</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -6309,7 +6425,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6339,35 +6455,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>6771.4499999999998</v>
+      </c>
+      <c r="N34" s="6">
+        <v>69</v>
+      </c>
+      <c r="O34" s="6">
+        <v>40</v>
+      </c>
+      <c r="P34" s="7">
+        <v>3.439613043478261</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>12.840417500000001</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.3951763157894739</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -6877,7 +7051,7 @@
         <v>19564</v>
       </c>
       <c r="B38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C38" s="4">
         <v>51</v>
@@ -6907,35 +7081,93 @@
         <v>58</v>
       </c>
       <c r="L38" s="4"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="8"/>
-      <c r="S38" s="8"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-      <c r="AA38" s="9"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
-      <c r="AD38" s="6"/>
-      <c r="AE38" s="6"/>
-      <c r="AF38" s="6"/>
-      <c r="AG38" s="6"/>
-      <c r="AH38" s="6"/>
-      <c r="AI38" s="6"/>
-      <c r="AJ38" s="6"/>
-      <c r="AK38" s="6"/>
-      <c r="AL38" s="6"/>
-      <c r="AM38" s="6"/>
-      <c r="AN38" s="9"/>
-      <c r="AO38" s="6"/>
+      <c r="M38" s="5">
+        <v>3437.5</v>
+      </c>
+      <c r="N38" s="6">
+        <v>46</v>
+      </c>
+      <c r="O38" s="6">
+        <v>31</v>
+      </c>
+      <c r="P38" s="7">
+        <v>4.0404755102040824</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>20.166667741935484</v>
+      </c>
+      <c r="R38" s="8">
+        <v>9.3268806451612907</v>
+      </c>
+      <c r="S38" s="8">
+        <v>7</v>
+      </c>
+      <c r="T38" s="9">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="U38" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="V38" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="W38" s="9">
+        <v>0</v>
+      </c>
+      <c r="X38" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="Y38" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE38" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF38" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP38" s="4">
         <v>58</v>
       </c>
@@ -6976,7 +7208,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7006,35 +7238,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>3987.9000000000001</v>
+      </c>
+      <c r="N39" s="6">
+        <v>47</v>
+      </c>
+      <c r="O39" s="6">
+        <v>32</v>
+      </c>
+      <c r="P39" s="7">
+        <v>2.9192021739130434</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>16.177603125000001</v>
+      </c>
+      <c r="R39" s="8">
+        <v>6.5827148148148149</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.53125</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.28125</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.21875</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7389,7 +7679,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7419,35 +7709,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>3350.9000000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>42</v>
+      </c>
+      <c r="O42" s="6">
+        <v>24</v>
+      </c>
+      <c r="P42" s="7">
+        <v>5.9594025641025636</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>24.981249999999999</v>
+      </c>
+      <c r="R42" s="8">
+        <v>11.828260869565218</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -8581,7 +8929,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8611,35 +8959,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>5361.4399999999996</v>
+      </c>
+      <c r="N50" s="6">
+        <v>62</v>
+      </c>
+      <c r="O50" s="6">
+        <v>35</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2.6754545454545458</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>14.416665714285715</v>
+      </c>
+      <c r="R50" s="8">
+        <v>4.3901031250000004</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.65714285714285714</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.31428571428571428</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -9248,7 +9654,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9278,35 +9684,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>4249.4099999999999</v>
+      </c>
+      <c r="N55" s="6">
+        <v>58</v>
+      </c>
+      <c r="O55" s="6">
+        <v>44</v>
+      </c>
+      <c r="P55" s="7">
+        <v>2.598360655737705</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>38.481818181818184</v>
+      </c>
+      <c r="R55" s="8">
+        <v>28.924243181818181</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.11363636363636363</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.068181818181818177</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9915,7 +10379,7 @@
         <v>19623</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C60" s="4">
         <v>51</v>
@@ -9945,35 +10409,93 @@
         <v>58</v>
       </c>
       <c r="L60" s="4"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="8"/>
-      <c r="S60" s="8"/>
-      <c r="T60" s="9"/>
-      <c r="U60" s="9"/>
-      <c r="V60" s="9"/>
-      <c r="W60" s="9"/>
-      <c r="X60" s="9"/>
-      <c r="Y60" s="9"/>
-      <c r="Z60" s="9"/>
-      <c r="AA60" s="9"/>
-      <c r="AB60" s="9"/>
-      <c r="AC60" s="9"/>
-      <c r="AD60" s="6"/>
-      <c r="AE60" s="6"/>
-      <c r="AF60" s="6"/>
-      <c r="AG60" s="6"/>
-      <c r="AH60" s="6"/>
-      <c r="AI60" s="6"/>
-      <c r="AJ60" s="6"/>
-      <c r="AK60" s="6"/>
-      <c r="AL60" s="6"/>
-      <c r="AM60" s="6"/>
-      <c r="AN60" s="9"/>
-      <c r="AO60" s="6"/>
+      <c r="M60" s="5">
+        <v>0</v>
+      </c>
+      <c r="N60" s="6">
+        <v>25</v>
+      </c>
+      <c r="O60" s="6">
+        <v>17</v>
+      </c>
+      <c r="P60" s="7">
+        <v>2.5209888888888887</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>15.083335294117646</v>
+      </c>
+      <c r="R60" s="8">
+        <v>5.2312500000000002</v>
+      </c>
+      <c r="S60" s="8">
+        <v>8</v>
+      </c>
+      <c r="T60" s="9">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="U60" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V60" s="9">
+        <v>0</v>
+      </c>
+      <c r="W60" s="9">
+        <v>0</v>
+      </c>
+      <c r="X60" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Y60" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Z60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AB60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE60" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI60" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP60" s="4">
         <v>58</v>
       </c>
@@ -11359,7 +11881,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>51</v>
@@ -11389,35 +11911,93 @@
         <v>58</v>
       </c>
       <c r="L70" s="4"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="8"/>
-      <c r="S70" s="8"/>
-      <c r="T70" s="9"/>
-      <c r="U70" s="9"/>
-      <c r="V70" s="9"/>
-      <c r="W70" s="9"/>
-      <c r="X70" s="9"/>
-      <c r="Y70" s="9"/>
-      <c r="Z70" s="9"/>
-      <c r="AA70" s="9"/>
-      <c r="AB70" s="9"/>
-      <c r="AC70" s="9"/>
-      <c r="AD70" s="6"/>
-      <c r="AE70" s="6"/>
-      <c r="AF70" s="6"/>
-      <c r="AG70" s="6"/>
-      <c r="AH70" s="6"/>
-      <c r="AI70" s="6"/>
-      <c r="AJ70" s="6"/>
-      <c r="AK70" s="6"/>
-      <c r="AL70" s="6"/>
-      <c r="AM70" s="6"/>
-      <c r="AN70" s="9"/>
-      <c r="AO70" s="6"/>
+      <c r="M70" s="5">
+        <v>2742.77</v>
+      </c>
+      <c r="N70" s="6">
+        <v>32</v>
+      </c>
+      <c r="O70" s="6">
+        <v>19</v>
+      </c>
+      <c r="P70" s="7">
+        <v>3.6838899999999999</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>15.059647368421054</v>
+      </c>
+      <c r="R70" s="8">
+        <v>4.8768500000000001</v>
+      </c>
+      <c r="S70" s="8">
+        <v>7</v>
+      </c>
+      <c r="T70" s="9">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="U70" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="V70" s="9">
+        <v>0</v>
+      </c>
+      <c r="W70" s="9">
+        <v>0</v>
+      </c>
+      <c r="X70" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y70" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AB70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP70" s="4">
         <v>58</v>
       </c>
@@ -12020,7 +12600,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -12050,35 +12630,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>3556.1500000000001</v>
+      </c>
+      <c r="N75" s="6">
+        <v>34</v>
+      </c>
+      <c r="O75" s="6">
+        <v>19</v>
+      </c>
+      <c r="P75" s="7">
+        <v>4.4732333333333338</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>18.206142105263158</v>
+      </c>
+      <c r="R75" s="8">
+        <v>6.9101833333333333</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.47368421052631576</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0.052631578946999998</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -13780,7 +14418,7 @@
         <v>19689</v>
       </c>
       <c r="B87" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C87" s="4">
         <v>51</v>
@@ -13810,35 +14448,93 @@
         <v>58</v>
       </c>
       <c r="L87" s="4"/>
-      <c r="M87" s="5"/>
-      <c r="N87" s="6"/>
-      <c r="O87" s="6"/>
-      <c r="P87" s="7"/>
-      <c r="Q87" s="8"/>
-      <c r="R87" s="8"/>
-      <c r="S87" s="8"/>
-      <c r="T87" s="9"/>
-      <c r="U87" s="9"/>
-      <c r="V87" s="9"/>
-      <c r="W87" s="9"/>
-      <c r="X87" s="9"/>
-      <c r="Y87" s="9"/>
-      <c r="Z87" s="9"/>
-      <c r="AA87" s="9"/>
-      <c r="AB87" s="9"/>
-      <c r="AC87" s="9"/>
-      <c r="AD87" s="6"/>
-      <c r="AE87" s="6"/>
-      <c r="AF87" s="6"/>
-      <c r="AG87" s="6"/>
-      <c r="AH87" s="6"/>
-      <c r="AI87" s="6"/>
-      <c r="AJ87" s="6"/>
-      <c r="AK87" s="6"/>
-      <c r="AL87" s="6"/>
-      <c r="AM87" s="6"/>
-      <c r="AN87" s="9"/>
-      <c r="AO87" s="6"/>
+      <c r="M87" s="5">
+        <v>2816.71</v>
+      </c>
+      <c r="N87" s="6">
+        <v>27</v>
+      </c>
+      <c r="O87" s="6">
+        <v>19</v>
+      </c>
+      <c r="P87" s="7">
+        <v>2.5970249999999999</v>
+      </c>
+      <c r="Q87" s="8">
+        <v>7.4508789473684205</v>
+      </c>
+      <c r="R87" s="8">
+        <v>4.5374999999999996</v>
+      </c>
+      <c r="S87" s="8">
+        <v>7</v>
+      </c>
+      <c r="T87" s="9">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="U87" s="9">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="V87" s="9">
+        <v>0</v>
+      </c>
+      <c r="W87" s="9">
+        <v>0</v>
+      </c>
+      <c r="X87" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="9">
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="Z87" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="9">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="AB87" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AC87" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="6">
+        <v>23</v>
+      </c>
+      <c r="AE87" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF87" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ87" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="6">
+        <v>15</v>
+      </c>
+      <c r="AL87" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM87" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP87" s="4">
         <v>58</v>
       </c>
@@ -14131,7 +14827,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -14161,35 +14857,93 @@
         <v>58</v>
       </c>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
-      <c r="S90" s="8"/>
-      <c r="T90" s="9"/>
-      <c r="U90" s="9"/>
-      <c r="V90" s="9"/>
-      <c r="W90" s="9"/>
-      <c r="X90" s="9"/>
-      <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-      <c r="AA90" s="9"/>
-      <c r="AB90" s="9"/>
-      <c r="AC90" s="9"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="6"/>
-      <c r="AN90" s="9"/>
-      <c r="AO90" s="6"/>
+      <c r="M90" s="5">
+        <v>2922.5799999999999</v>
+      </c>
+      <c r="N90" s="6">
+        <v>31</v>
+      </c>
+      <c r="O90" s="6">
+        <v>21</v>
+      </c>
+      <c r="P90" s="7">
+        <v>6.3706896551724137</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>25.130157142857144</v>
+      </c>
+      <c r="R90" s="8">
+        <v>11.497619047619047</v>
+      </c>
+      <c r="S90" s="8">
+        <v>7</v>
+      </c>
+      <c r="T90" s="9">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="U90" s="9">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="V90" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="W90" s="9">
+        <v>0</v>
+      </c>
+      <c r="X90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AC90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
       </c>
@@ -14230,7 +14984,7 @@
         <v>19698</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C91" s="4">
         <v>51</v>
@@ -14260,35 +15014,93 @@
         <v>58</v>
       </c>
       <c r="L91" s="4"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="6"/>
-      <c r="O91" s="6"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="8"/>
-      <c r="R91" s="8"/>
-      <c r="S91" s="8"/>
-      <c r="T91" s="9"/>
-      <c r="U91" s="9"/>
-      <c r="V91" s="9"/>
-      <c r="W91" s="9"/>
-      <c r="X91" s="9"/>
-      <c r="Y91" s="9"/>
-      <c r="Z91" s="9"/>
-      <c r="AA91" s="9"/>
-      <c r="AB91" s="9"/>
-      <c r="AC91" s="9"/>
-      <c r="AD91" s="6"/>
-      <c r="AE91" s="6"/>
-      <c r="AF91" s="6"/>
-      <c r="AG91" s="6"/>
-      <c r="AH91" s="6"/>
-      <c r="AI91" s="6"/>
-      <c r="AJ91" s="6"/>
-      <c r="AK91" s="6"/>
-      <c r="AL91" s="6"/>
-      <c r="AM91" s="6"/>
-      <c r="AN91" s="9"/>
-      <c r="AO91" s="6"/>
+      <c r="M91" s="5">
+        <v>0</v>
+      </c>
+      <c r="N91" s="6">
+        <v>50</v>
+      </c>
+      <c r="O91" s="6">
+        <v>35</v>
+      </c>
+      <c r="P91" s="7">
+        <v>7.2443340000000003</v>
+      </c>
+      <c r="Q91" s="8">
+        <v>20.854902941176469</v>
+      </c>
+      <c r="R91" s="8">
+        <v>5.7681818181818176</v>
+      </c>
+      <c r="S91" s="8">
+        <v>7</v>
+      </c>
+      <c r="T91" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="U91" s="9">
+        <v>0.085714285714285715</v>
+      </c>
+      <c r="V91" s="9">
+        <v>0</v>
+      </c>
+      <c r="W91" s="9">
+        <v>0</v>
+      </c>
+      <c r="X91" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AA91" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AB91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE91" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK91" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP91" s="4">
         <v>58</v>
       </c>
@@ -15050,7 +15862,7 @@
         <v>19710</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>51</v>
@@ -15080,35 +15892,93 @@
         <v>58</v>
       </c>
       <c r="L97" s="4"/>
-      <c r="M97" s="5"/>
-      <c r="N97" s="6"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="7"/>
-      <c r="Q97" s="8"/>
-      <c r="R97" s="8"/>
-      <c r="S97" s="8"/>
-      <c r="T97" s="9"/>
-      <c r="U97" s="9"/>
-      <c r="V97" s="9"/>
-      <c r="W97" s="9"/>
-      <c r="X97" s="9"/>
-      <c r="Y97" s="9"/>
-      <c r="Z97" s="9"/>
-      <c r="AA97" s="9"/>
-      <c r="AB97" s="9"/>
-      <c r="AC97" s="9"/>
-      <c r="AD97" s="6"/>
-      <c r="AE97" s="6"/>
-      <c r="AF97" s="6"/>
-      <c r="AG97" s="6"/>
-      <c r="AH97" s="6"/>
-      <c r="AI97" s="6"/>
-      <c r="AJ97" s="6"/>
-      <c r="AK97" s="6"/>
-      <c r="AL97" s="6"/>
-      <c r="AM97" s="6"/>
-      <c r="AN97" s="9"/>
-      <c r="AO97" s="6"/>
+      <c r="M97" s="5">
+        <v>2195.3000000000002</v>
+      </c>
+      <c r="N97" s="6">
+        <v>37</v>
+      </c>
+      <c r="O97" s="6">
+        <v>14</v>
+      </c>
+      <c r="P97" s="7">
+        <v>4.4970249999999998</v>
+      </c>
+      <c r="Q97" s="8">
+        <v>14.302378571428573</v>
+      </c>
+      <c r="R97" s="8">
+        <v>3.2388916666666669</v>
+      </c>
+      <c r="S97" s="8">
+        <v>6</v>
+      </c>
+      <c r="T97" s="9">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U97" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V97" s="9">
+        <v>0</v>
+      </c>
+      <c r="W97" s="9">
+        <v>0</v>
+      </c>
+      <c r="X97" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AB97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE97" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP97" s="4">
         <v>58</v>
       </c>
@@ -19235,7 +20105,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>51</v>
@@ -19265,35 +20135,93 @@
         <v>58</v>
       </c>
       <c r="L126" s="4"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="9"/>
-      <c r="U126" s="9"/>
-      <c r="V126" s="9"/>
-      <c r="W126" s="9"/>
-      <c r="X126" s="9"/>
-      <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-      <c r="AA126" s="9"/>
-      <c r="AB126" s="9"/>
-      <c r="AC126" s="9"/>
-      <c r="AD126" s="6"/>
-      <c r="AE126" s="6"/>
-      <c r="AF126" s="6"/>
-      <c r="AG126" s="6"/>
-      <c r="AH126" s="6"/>
-      <c r="AI126" s="6"/>
-      <c r="AJ126" s="6"/>
-      <c r="AK126" s="6"/>
-      <c r="AL126" s="6"/>
-      <c r="AM126" s="6"/>
-      <c r="AN126" s="9"/>
-      <c r="AO126" s="6"/>
+      <c r="M126" s="5">
+        <v>1647.53</v>
+      </c>
+      <c r="N126" s="6">
+        <v>22</v>
+      </c>
+      <c r="O126" s="6">
+        <v>16</v>
+      </c>
+      <c r="P126" s="7">
+        <v>4.5856045454545455</v>
+      </c>
+      <c r="Q126" s="8">
+        <v>48.557293749999999</v>
+      </c>
+      <c r="R126" s="8">
+        <v>36.616668750000002</v>
+      </c>
+      <c r="S126" s="8">
+        <v>7</v>
+      </c>
+      <c r="T126" s="9">
+        <v>0</v>
+      </c>
+      <c r="U126" s="9">
+        <v>0</v>
+      </c>
+      <c r="V126" s="9">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9">
+        <v>0</v>
+      </c>
+      <c r="X126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO126" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
       </c>
@@ -21470,7 +22398,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -21500,35 +22428,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>2152.7800000000002</v>
+      </c>
+      <c r="N141" s="6">
+        <v>23</v>
+      </c>
+      <c r="O141" s="6">
+        <v>13</v>
+      </c>
+      <c r="P141" s="7">
+        <v>3.9130434782608696</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>18.065384615384616</v>
+      </c>
+      <c r="R141" s="8">
+        <v>5.8782076923076927</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -24056,7 +25042,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -24086,35 +25072,93 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
-      <c r="O159" s="6"/>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
-      <c r="S159" s="8"/>
-      <c r="T159" s="9"/>
-      <c r="U159" s="9"/>
-      <c r="V159" s="9"/>
-      <c r="W159" s="9"/>
-      <c r="X159" s="9"/>
-      <c r="Y159" s="9"/>
-      <c r="Z159" s="9"/>
-      <c r="AA159" s="9"/>
-      <c r="AB159" s="9"/>
-      <c r="AC159" s="9"/>
-      <c r="AD159" s="6"/>
-      <c r="AE159" s="6"/>
-      <c r="AF159" s="6"/>
-      <c r="AG159" s="6"/>
-      <c r="AH159" s="6"/>
-      <c r="AI159" s="6"/>
-      <c r="AJ159" s="6"/>
-      <c r="AK159" s="6"/>
-      <c r="AL159" s="6"/>
-      <c r="AM159" s="6"/>
-      <c r="AN159" s="9"/>
-      <c r="AO159" s="6"/>
+      <c r="M159" s="5">
+        <v>4366.5500000000002</v>
+      </c>
+      <c r="N159" s="6">
+        <v>49</v>
+      </c>
+      <c r="O159" s="6">
+        <v>34</v>
+      </c>
+      <c r="P159" s="7">
+        <v>4.1072916666666668</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>17.699020588235296</v>
+      </c>
+      <c r="R159" s="8">
+        <v>6.4357852941176468</v>
+      </c>
+      <c r="S159" s="8">
+        <v>7</v>
+      </c>
+      <c r="T159" s="9">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="U159" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="V159" s="9">
+        <v>0</v>
+      </c>
+      <c r="W159" s="9">
+        <v>0</v>
+      </c>
+      <c r="X159" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AC159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO159" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP159" s="4">
         <v>58</v>
       </c>
@@ -26289,7 +27333,7 @@
         <v>19894</v>
       </c>
       <c r="B174" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C174" s="4">
         <v>51</v>
@@ -26319,35 +27363,93 @@
         <v>58</v>
       </c>
       <c r="L174" s="4"/>
-      <c r="M174" s="5"/>
-      <c r="N174" s="6"/>
-      <c r="O174" s="6"/>
-      <c r="P174" s="7"/>
-      <c r="Q174" s="8"/>
-      <c r="R174" s="8"/>
-      <c r="S174" s="8"/>
-      <c r="T174" s="9"/>
-      <c r="U174" s="9"/>
-      <c r="V174" s="9"/>
-      <c r="W174" s="9"/>
-      <c r="X174" s="9"/>
-      <c r="Y174" s="9"/>
-      <c r="Z174" s="9"/>
-      <c r="AA174" s="9"/>
-      <c r="AB174" s="9"/>
-      <c r="AC174" s="9"/>
-      <c r="AD174" s="6"/>
-      <c r="AE174" s="6"/>
-      <c r="AF174" s="6"/>
-      <c r="AG174" s="6"/>
-      <c r="AH174" s="6"/>
-      <c r="AI174" s="6"/>
-      <c r="AJ174" s="6"/>
-      <c r="AK174" s="6"/>
-      <c r="AL174" s="6"/>
-      <c r="AM174" s="6"/>
-      <c r="AN174" s="9"/>
-      <c r="AO174" s="6"/>
+      <c r="M174" s="5">
+        <v>3797.8499999999999</v>
+      </c>
+      <c r="N174" s="6">
+        <v>44</v>
+      </c>
+      <c r="O174" s="6">
+        <v>32</v>
+      </c>
+      <c r="P174" s="7">
+        <v>5.2410560975609757</v>
+      </c>
+      <c r="Q174" s="8">
+        <v>15.224478124999999</v>
+      </c>
+      <c r="R174" s="8">
+        <v>2.8869781250000002</v>
+      </c>
+      <c r="S174" s="8">
+        <v>7</v>
+      </c>
+      <c r="T174" s="9">
+        <v>0.5625</v>
+      </c>
+      <c r="U174" s="9">
+        <v>0.15625</v>
+      </c>
+      <c r="V174" s="9">
+        <v>0</v>
+      </c>
+      <c r="W174" s="9">
+        <v>0</v>
+      </c>
+      <c r="X174" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y174" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z174" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA174" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AB174" s="9">
+        <v>0.09375</v>
+      </c>
+      <c r="AC174" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD174" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE174" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF174" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG174" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH174" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI174" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ174" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK174" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL174" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM174" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN174" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO174" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP174" s="4">
         <v>58</v>
       </c>
@@ -26386,7 +27488,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -26416,35 +27518,93 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
-      <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="M175" s="5">
+        <v>3392.8299999999999</v>
+      </c>
+      <c r="N175" s="6">
+        <v>50</v>
+      </c>
+      <c r="O175" s="6">
+        <v>33</v>
+      </c>
+      <c r="P175" s="7">
+        <v>5.8962955555555556</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>18.642930303030301</v>
+      </c>
+      <c r="R175" s="8">
+        <v>6.0442718749999997</v>
+      </c>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
+      <c r="T175" s="9">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="U175" s="9">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -27520,7 +28680,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>51</v>
@@ -27550,35 +28710,93 @@
         <v>58</v>
       </c>
       <c r="L183" s="4"/>
-      <c r="M183" s="5"/>
-      <c r="N183" s="6"/>
-      <c r="O183" s="6"/>
-      <c r="P183" s="7"/>
-      <c r="Q183" s="8"/>
-      <c r="R183" s="8"/>
-      <c r="S183" s="8"/>
-      <c r="T183" s="9"/>
-      <c r="U183" s="9"/>
-      <c r="V183" s="9"/>
-      <c r="W183" s="9"/>
-      <c r="X183" s="9"/>
-      <c r="Y183" s="9"/>
-      <c r="Z183" s="9"/>
-      <c r="AA183" s="9"/>
-      <c r="AB183" s="9"/>
-      <c r="AC183" s="9"/>
-      <c r="AD183" s="6"/>
-      <c r="AE183" s="6"/>
-      <c r="AF183" s="6"/>
-      <c r="AG183" s="6"/>
-      <c r="AH183" s="6"/>
-      <c r="AI183" s="6"/>
-      <c r="AJ183" s="6"/>
-      <c r="AK183" s="6"/>
-      <c r="AL183" s="6"/>
-      <c r="AM183" s="6"/>
-      <c r="AN183" s="9"/>
-      <c r="AO183" s="6"/>
+      <c r="M183" s="5">
+        <v>3073.5</v>
+      </c>
+      <c r="N183" s="6">
+        <v>37</v>
+      </c>
+      <c r="O183" s="6">
+        <v>29</v>
+      </c>
+      <c r="P183" s="7">
+        <v>5.7247756756756756</v>
+      </c>
+      <c r="Q183" s="8">
+        <v>16.493679310344827</v>
+      </c>
+      <c r="R183" s="8">
+        <v>3.2602576923076922</v>
+      </c>
+      <c r="S183" s="8">
+        <v>8</v>
+      </c>
+      <c r="T183" s="9">
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="U183" s="9">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="V183" s="9">
+        <v>0</v>
+      </c>
+      <c r="W183" s="9">
+        <v>0</v>
+      </c>
+      <c r="X183" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y183" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="9">
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="AB183" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AC183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD183" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH183" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK183" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL183" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO183" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP183" s="4">
         <v>58</v>
       </c>
@@ -27974,7 +29192,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -28004,35 +29222,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>505.24000000000001</v>
+      </c>
+      <c r="N187" s="6">
+        <v>6</v>
+      </c>
+      <c r="O187" s="6">
+        <v>5</v>
+      </c>
+      <c r="P187" s="7">
+        <v>7.9972166666666666</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>22.50666</v>
+      </c>
+      <c r="R187" s="8">
+        <v>7.4833400000000001</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -28230,7 +29506,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -28260,35 +29536,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>4052.0300000000002</v>
+      </c>
+      <c r="N189" s="6">
+        <v>55</v>
+      </c>
+      <c r="O189" s="6">
+        <v>51</v>
+      </c>
+      <c r="P189" s="7">
+        <v>4.7307465517241383</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>23.023201960784313</v>
+      </c>
+      <c r="R189" s="8">
+        <v>11.397711764705884</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.098039215686274508</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.49019607843137253</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>25</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>25</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>21</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -28329,7 +29663,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28359,35 +29693,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>3901.9099999999999</v>
+      </c>
+      <c r="N190" s="6">
+        <v>37</v>
+      </c>
+      <c r="O190" s="6">
+        <v>25</v>
+      </c>
+      <c r="P190" s="7">
+        <v>5.1476861111111107</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>20.105999999999998</v>
+      </c>
+      <c r="R190" s="8">
+        <v>7.8760000000000003</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -29839,7 +31231,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29869,35 +31261,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>731.97000000000003</v>
+      </c>
+      <c r="N200" s="6">
+        <v>10</v>
+      </c>
+      <c r="O200" s="6">
+        <v>3</v>
+      </c>
+      <c r="P200" s="7">
+        <v>5.3733300000000002</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>22.483333333333334</v>
+      </c>
+      <c r="R200" s="8">
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0.33333333333300003</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -30764,7 +32214,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -30794,35 +32244,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>1998.04</v>
+      </c>
+      <c r="N207" s="6">
+        <v>23</v>
+      </c>
+      <c r="O207" s="6">
+        <v>8</v>
+      </c>
+      <c r="P207" s="7">
+        <v>6.1246391304347831</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>23.139587500000001</v>
+      </c>
+      <c r="R207" s="8">
+        <v>9.875</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 4.054,39</t>
-  </si>
-  <si>
-    <t>44.7</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>4.71</t>
-  </si>
-  <si>
-    <t>18.9</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 4.048,49</t>
+  </si>
+  <si>
+    <t>44.6</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>4.73</t>
+  </si>
+  <si>
+    <t>18.8</t>
   </si>
   <si>
     <t>7.5</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>44.6%</t>
-  </si>
-  <si>
-    <t>18.2%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>44.5%</t>
+  </si>
+  <si>
+    <t>18.5%</t>
   </si>
   <si>
     <t>1.8%</t>
@@ -974,49 +974,49 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.4%</t>
+    <t>5.3%</t>
   </si>
   <si>
     <t>1.3%</t>
   </si>
   <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
+    <t>7.2%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
   </si>
   <si>
     <t>4.3%</t>
   </si>
   <si>
-    <t>1171.0</t>
-  </si>
-  <si>
-    <t>940.0</t>
-  </si>
-  <si>
-    <t>91.0</t>
+    <t>1214.0</t>
+  </si>
+  <si>
+    <t>977.0</t>
+  </si>
+  <si>
+    <t>94.0</t>
   </si>
   <si>
     <t>11.0</t>
   </si>
   <si>
-    <t>279.0</t>
-  </si>
-  <si>
-    <t>67.0</t>
+    <t>280.0</t>
+  </si>
+  <si>
+    <t>70.0</t>
   </si>
   <si>
     <t>9.0</t>
   </si>
   <si>
-    <t>347.0</t>
-  </si>
-  <si>
-    <t>133.0</t>
-  </si>
-  <si>
-    <t>223.0</t>
+    <t>380.0</t>
+  </si>
+  <si>
+    <t>134.0</t>
+  </si>
+  <si>
+    <t>225.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -3278,7 +3278,9 @@
       <c r="N13" s="6">
         <v>63</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>49</v>
+      </c>
       <c r="P13" s="7">
         <v>12.368011290322579</v>
       </c>
@@ -3288,31 +3290,75 @@
       <c r="R13" s="8">
         <v>8.3329938775510204</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.020408163265306121</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.061224489795918366</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -16643,7 +16689,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16673,35 +16719,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>3131.4899999999998</v>
+      </c>
+      <c r="N102" s="6">
+        <v>36</v>
+      </c>
+      <c r="O102" s="6">
+        <v>28</v>
+      </c>
+      <c r="P102" s="7">
+        <v>8.5991</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>13.471428571428572</v>
+      </c>
+      <c r="R102" s="8">
+        <v>2.0192307692307692</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>22</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>18</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -28424,7 +28528,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -28454,35 +28558,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>3892.8400000000001</v>
+      </c>
+      <c r="N181" s="6">
+        <v>35</v>
+      </c>
+      <c r="O181" s="6">
+        <v>24</v>
+      </c>
+      <c r="P181" s="7">
+        <v>4.2128571428571426</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>10.802083333333334</v>
+      </c>
+      <c r="R181" s="8">
+        <v>3.5592555555555552</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.875</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>15</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
@@ -938,31 +938,31 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 4.048,49</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 4.045,01</t>
   </si>
   <si>
     <t>44.6</t>
   </si>
   <si>
-    <t>28.4</t>
-  </si>
-  <si>
-    <t>4.73</t>
-  </si>
-  <si>
-    <t>18.8</t>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>4.74</t>
+  </si>
+  <si>
+    <t>18.9</t>
   </si>
   <si>
     <t>7.5</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>44.5%</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>44.4%</t>
   </si>
   <si>
     <t>18.5%</t>
@@ -14776,7 +14776,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14804,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>3404.0500000000002</v>
+      </c>
+      <c r="N89" s="6">
+        <v>38</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>6.7222230769230764</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>26.812961111111111</v>
+      </c>
+      <c r="R89" s="8">
+        <v>12.223529411764707</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.1111111111111111</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -18735,33 +18747,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>14</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -29098,7 +29156,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31806,7 +31864,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-14).xlsx
@@ -938,19 +938,19 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 4.045,01</t>
+    <t>R$ 4.023,93</t>
   </si>
   <si>
-    <t>44.6</t>
+    <t>44.2</t>
   </si>
   <si>
     <t>28.3</t>
   </si>
   <si>
-    <t>4.74</t>
+    <t>4.77</t>
   </si>
   <si>
     <t>18.9</t>
@@ -959,40 +959,40 @@
     <t>7.5</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.5</t>
   </si>
   <si>
     <t>44.4%</t>
   </si>
   <si>
-    <t>18.5%</t>
+    <t>18.1%</t>
   </si>
   <si>
-    <t>1.8%</t>
+    <t>1.7%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.3%</t>
+    <t>5.1%</t>
   </si>
   <si>
     <t>1.3%</t>
   </si>
   <si>
-    <t>7.2%</t>
+    <t>7.0%</t>
   </si>
   <si>
     <t>2.5%</t>
   </si>
   <si>
-    <t>4.3%</t>
+    <t>4.2%</t>
   </si>
   <si>
-    <t>1214.0</t>
+    <t>1224.0</t>
   </si>
   <si>
-    <t>977.0</t>
+    <t>987.0</t>
   </si>
   <si>
     <t>94.0</t>
@@ -1001,22 +1001,22 @@
     <t>11.0</t>
   </si>
   <si>
-    <t>280.0</t>
+    <t>281.0</t>
   </si>
   <si>
     <t>70.0</t>
   </si>
   <si>
-    <t>9.0</t>
+    <t>10.0</t>
   </si>
   <si>
-    <t>380.0</t>
+    <t>382.0</t>
   </si>
   <si>
-    <t>134.0</t>
+    <t>138.0</t>
   </si>
   <si>
-    <t>225.0</t>
+    <t>227.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>9467</v>
+      </c>
+      <c r="N6" s="6">
+        <v>96</v>
+      </c>
+      <c r="O6" s="6">
+        <v>75</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5.894148936170212</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>16.207333333333334</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.0746666666666664</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.49333333333333335</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0.026666666666666668</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9132,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9220,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1182.0899999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>11</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>6.0333363636363631</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>28.800000000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>18.233340000000002</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10201,33 +10271,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>28</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24124,7 +24240,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24154,35 +24270,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2117.3499999999999</v>
+      </c>
+      <c r="N151" s="6">
+        <v>28</v>
+      </c>
+      <c r="O151" s="6">
+        <v>21</v>
+      </c>
+      <c r="P151" s="7">
+        <v>3.6136892857142859</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>13.580157142857141</v>
+      </c>
+      <c r="R151" s="8">
+        <v>3.0166666666666666</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25006,7 +25180,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25036,35 +25210,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>1698.3599999999999</v>
+      </c>
+      <c r="N157" s="6">
+        <v>19</v>
+      </c>
+      <c r="O157" s="6">
+        <v>13</v>
+      </c>
+      <c r="P157" s="7">
+        <v>7.5166666666666675</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>19.428207692307691</v>
+      </c>
+      <c r="R157" s="8">
+        <v>4.2512846153846153</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25105,7 +25337,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25135,35 +25367,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2438.25</v>
+      </c>
+      <c r="N158" s="6">
+        <v>22</v>
+      </c>
+      <c r="O158" s="6">
+        <v>21</v>
+      </c>
+      <c r="P158" s="7">
+        <v>6.4053045454545448</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>18.854761904761904</v>
+      </c>
+      <c r="R158" s="8">
+        <v>5.4761904761904763</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26140,7 +26430,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26170,35 +26460,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>3340.1100000000001</v>
+      </c>
+      <c r="N165" s="6">
+        <v>33</v>
+      </c>
+      <c r="O165" s="6">
+        <v>16</v>
+      </c>
+      <c r="P165" s="7">
+        <v>4.8762636363636362</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>13.975</v>
+      </c>
+      <c r="R165" s="8">
+        <v>1.9645812499999999</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
